--- a/output/pdf_financials_xlsx/ACD.xlsx
+++ b/output/pdf_financials_xlsx/ACD.xlsx
@@ -2670,20 +2670,14 @@
       <c r="E32" s="3" t="n">
         <v>9.387722999999999</v>
       </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F32" s="3" t="n">
+        <v>8.894246000000001</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>8.403725</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>8.221498</v>
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ACD.xlsx
+++ b/output/pdf_financials_xlsx/ACD.xlsx
@@ -737,17 +737,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>24.087</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>35.299</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>36.006</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>33.191</v>
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3755,16 +3763,16 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>9899015</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0</v>
+        <v>993.723</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0</v>
+        <v>339.267</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>4541.155</v>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
@@ -3772,43 +3780,43 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0</v>
+        <v>3442186</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>3442.186</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0</v>
+        <v>7103.273</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0</v>
+        <v>12440.143</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0</v>
+        <v>12772.906</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0</v>
+        <v>12457</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>0</v>
+        <v>16.345848</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0</v>
+        <v>6.776422</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0</v>
+        <v>13.839291</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0</v>
+        <v>11.63</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0</v>
+        <v>5.914</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>0</v>
+        <v>16.674</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="47">
@@ -3881,16 +3889,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>9899015</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>993.723</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0</v>
+        <v>339.267</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>4541.155</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -3898,43 +3906,43 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>3442186</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>3442.186</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>7103.273</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>12440.143</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0</v>
+        <v>12772.906</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0</v>
+        <v>12457</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0</v>
+        <v>16.345848</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0</v>
+        <v>6.776422</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0</v>
+        <v>13.839291</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0</v>
+        <v>11.63</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0</v>
+        <v>5.914</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0</v>
+        <v>16.674</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="49">
@@ -10911,7 +10919,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -30833,7 +30841,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -32921,7 +32929,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -53051,7 +53059,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">

--- a/output/pdf_financials_xlsx/ACD.xlsx
+++ b/output/pdf_financials_xlsx/ACD.xlsx
@@ -2834,16 +2834,16 @@
         <v>111.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>577.164</v>
+        <v>451.241</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>711.3</v>
+        <v>575.552</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>663.045</v>
+        <v>509.524</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>547.665</v>
+        <v>386.734</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.410229</v>
@@ -2864,7 +2864,7 @@
         <v>0.104</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="35">
@@ -2897,16 +2897,16 @@
         <v>9877.811</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>10801.451</v>
+        <v>10675.528</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>11409.915</v>
+        <v>11274.167</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>7807.497</v>
+        <v>7653.976</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>7149.953</v>
+        <v>6989.022</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>11.741682</v>
@@ -2929,7 +2929,7 @@
         <v>-2.989</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-23.772</v>
+        <v>-23.285</v>
       </c>
     </row>
     <row r="36">
@@ -3014,7 +3014,7 @@
         <v>-3.598776728953959</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-38.40511809751527</v>
+        <v>-37.6183398494297</v>
       </c>
     </row>
     <row r="37">
@@ -8303,37 +8303,37 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>451.241</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>575.552</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>509.524</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>386.734</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.688743</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>1.026735</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.83634</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.834</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="116">
@@ -9071,22 +9071,22 @@
         <v>0</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>0</v>
+        <v>0.002941</v>
       </c>
       <c r="N127" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O127" s="3" t="n">
-        <v>0</v>
+        <v>0.004041</v>
       </c>
       <c r="P127" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="R127" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="S127" s="3" t="n">
         <v>0</v>
@@ -34381,7 +34381,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -34477,7 +34477,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -34577,7 +34581,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -37851,7 +37859,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -37957,7 +37965,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -40845,7 +40857,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -40951,7 +40963,11 @@
           <t>Depreciation of property and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -53475,7 +53491,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -55071,7 +55087,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -58577,7 +58593,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -60047,7 +60063,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -61725,7 +61741,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
